--- a/Specifications/Risk_Traceability_Matrix.xlsx
+++ b/Specifications/Risk_Traceability_Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NoordWes Universiteit\Mechatronics Engineering\Jaar 3\Semester 2\MCTR327\Eng_DesignProject_GantryCrane_Group-18\Specifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E091AAEB-E4D9-475A-B69B-89A061A07F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C587BAA-33EE-45CB-B4E4-C5BCF3D9B3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CE4302D-EC5D-4A58-A53C-426CE452EC11}"/>
   </bookViews>
@@ -38,9 +38,207 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="58">
+  <si>
+    <t>Table 24  Risk Traceability Matrix BEFORE Mitigation</t>
+  </si>
+  <si>
+    <t>Risk Codes</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>K1</t>
+  </si>
+  <si>
+    <t>K2</t>
+  </si>
+  <si>
+    <t>Score legend:</t>
+  </si>
+  <si>
+    <t>1 – 4   Low risk</t>
+  </si>
+  <si>
+    <t>5 – 9   Moderate risk</t>
+  </si>
+  <si>
+    <t>10 – 14  High risk</t>
+  </si>
+  <si>
+    <t>≥ 15   Critical risk</t>
+  </si>
+  <si>
+    <t>Instructions: Fill in Likelihood (1–5) and Impact (1–5) values in the light-blue cells. Leave cells blank if that risk category does not apply to the risk code. Score = Likelihood × Impact and is coloured automatically.</t>
+  </si>
+  <si>
+    <t>Knowledge Risk
+Score</t>
+  </si>
+  <si>
+    <t>Technical Risk
+Score</t>
+  </si>
+  <si>
+    <t>Logistic Risk
+Score</t>
+  </si>
+  <si>
+    <t>Schedule Risk
+Score</t>
+  </si>
+  <si>
+    <t>Knowledge Risk
+Impact</t>
+  </si>
+  <si>
+    <t>Knowledge Risk
+Likelihood</t>
+  </si>
+  <si>
+    <t>Technical Risk
+Impact</t>
+  </si>
+  <si>
+    <t>Technical Risk
+Likelihood</t>
+  </si>
+  <si>
+    <t>Logistic Risk
+Impact</t>
+  </si>
+  <si>
+    <t>Logistic Risk
+Likelihood</t>
+  </si>
+  <si>
+    <t>Schedule Risk
+Impact</t>
+  </si>
+  <si>
+    <t>Schedule Risk
+Likelihood</t>
+  </si>
+  <si>
+    <t>Table 25  Risk Traceability Matrix AFTER Mitigation</t>
+  </si>
+  <si>
+    <t>≥ 15     Critical risk</t>
+  </si>
+  <si>
+    <t>5 – 9    Moderate risk</t>
+  </si>
+  <si>
+    <t>1 – 4    Low risk</t>
+  </si>
+  <si>
+    <t>Score colour scale:</t>
+  </si>
+  <si>
+    <t>To embed this table in your LaTeX report: install the Excel2LaTeX add-in, select the table range, and click Convert to LaTeX. Paste the output into content/B_risk_register.tex.</t>
+  </si>
+  <si>
+    <t>Excel2LaTeX export</t>
+  </si>
+  <si>
+    <t>Click the last data row, copy it (Ctrl+C), then paste below. All formulas and formatting will be replicated. Update the Risk Code in column A.</t>
+  </si>
+  <si>
+    <t>Adding rows</t>
+  </si>
+  <si>
+    <t>Fill in BEFORE Mitigation first. After defining mitigations, copy the risk codes to AFTER Mitigation and enter the revised likelihood and impact values to show the improvement.</t>
+  </si>
+  <si>
+    <t>BEFORE / AFTER sheets</t>
+  </si>
+  <si>
+    <t>Leave a cell blank if that risk category does not apply to that risk code. The score cell will remain empty automatically.</t>
+  </si>
+  <si>
+    <t>Blank cells</t>
+  </si>
+  <si>
+    <t>Calculated automatically as Likelihood × Impact. The cell colour updates via conditional formatting:
+  Green (1–4): Low    Yellow (5–9): Moderate    Orange (10–14): High    Red (≥15): Critical</t>
+  </si>
+  <si>
+    <t>Score (auto)</t>
+  </si>
+  <si>
+    <t>Rate the consequence if the risk materialises:
+  1 = Negligible   2 = Minor   3 = Moderate   4 = Major   5 = Severe</t>
+  </si>
+  <si>
+    <t>Impact (1–5)</t>
+  </si>
+  <si>
+    <t>Rate how likely the risk is to occur:
+  1 = Very Low   2 = Low   3 = Medium   4 = High   5 = Very High</t>
+  </si>
+  <si>
+    <t>Likelihood (1–5)</t>
+  </si>
+  <si>
+    <t>Enter a unique identifier for each risk (e.g. S1, S2 for Schedule risks; L1 for Logistic; T1, T2 for Technical; K1, K2 for Knowledge). Add rows by copying a data row down.</t>
+  </si>
+  <si>
+    <t>NWU Risk Traceability Matrix – How to Use</t>
+  </si>
+  <si>
+    <t>Group Risk Impact</t>
+  </si>
+  <si>
+    <t>Group Risk Likelihood</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P Risk
+Likelihood</t>
+  </si>
+  <si>
+    <t>P Risk
+Impact</t>
+  </si>
+  <si>
+    <t>Logistical Risk
+Likelihood</t>
+  </si>
+  <si>
+    <t>Logistical Risk
+Impact</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -48,16 +246,147 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FF993300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8C00"/>
+        <bgColor rgb="FFFF6600"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD700"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FF008080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF0066CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,17 +394,184 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD700"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF8C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD700"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF8C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -405,9 +901,911 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEDE8F47-BC4B-4B60-A383-ABA60BBBE1EE}">
-  <dimension ref="A1"/>
+  <dimension ref="B3:U60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="4.77734375" customWidth="1"/>
+    <col min="4" max="6" width="5" customWidth="1"/>
+    <col min="7" max="7" width="5.44140625" customWidth="1"/>
+    <col min="8" max="8" width="4.88671875" customWidth="1"/>
+    <col min="9" max="10" width="4.5546875" customWidth="1"/>
+    <col min="11" max="11" width="4.6640625" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="13" max="13" width="5" customWidth="1"/>
+    <col min="14" max="14" width="4.33203125" customWidth="1"/>
+    <col min="15" max="15" width="5.109375" customWidth="1"/>
+    <col min="16" max="16" width="6.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+    </row>
+    <row r="4" spans="2:16" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B5" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="9">
+        <v>5</v>
+      </c>
+      <c r="D5" s="9">
+        <v>4</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="12">
+        <f t="shared" ref="M5:M13" si="0">IF(AND(C5&lt;&gt;"",D5&lt;&gt;""),C5*D5,"")</f>
+        <v>20</v>
+      </c>
+      <c r="N5" s="8" t="str">
+        <f t="shared" ref="N5:N13" si="1">IF(AND(G5&lt;&gt;"",H5&lt;&gt;""),G5*H5,"")</f>
+        <v/>
+      </c>
+      <c r="O5" s="8" t="str">
+        <f t="shared" ref="O5:O13" si="2">IF(AND(I5&lt;&gt;"",J5&lt;&gt;""),I5*J5,"")</f>
+        <v/>
+      </c>
+      <c r="P5" s="8" t="str">
+        <f t="shared" ref="P5:P13" si="3">IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),K5*L5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B6" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="9">
+        <v>2</v>
+      </c>
+      <c r="D6" s="9">
+        <v>3</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="13">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="N6" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O6" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P6" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="9">
+        <v>3</v>
+      </c>
+      <c r="H9" s="9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N9" s="7">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="O9" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P9" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B10" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="10">
+        <v>4</v>
+      </c>
+      <c r="J10" s="10">
+        <v>4</v>
+      </c>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N10" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O10" s="12">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="P10" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B11" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="9">
+        <v>3</v>
+      </c>
+      <c r="J11" s="9">
+        <v>5</v>
+      </c>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N11" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O11" s="12">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="P11" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B12" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="9">
+        <v>3</v>
+      </c>
+      <c r="L12" s="9">
+        <v>4</v>
+      </c>
+      <c r="M12" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N12" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O12" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P12" s="7">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B13" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="9">
+        <v>3</v>
+      </c>
+      <c r="L13" s="9">
+        <v>4</v>
+      </c>
+      <c r="M13" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N13" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O13" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P13" s="7">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B17" s="5"/>
+      <c r="C17" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B18" s="4"/>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B19" s="3"/>
+      <c r="C19" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B20" s="2"/>
+      <c r="C20" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B22" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B25" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="23"/>
+    </row>
+    <row r="26" spans="2:16" ht="65.400000000000006" x14ac:dyDescent="0.3">
+      <c r="B26" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M26" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="O26" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="P26" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B27" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="9">
+        <v>2</v>
+      </c>
+      <c r="D27" s="9">
+        <v>4</v>
+      </c>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="13">
+        <f t="shared" ref="M27:M33" si="4">IF(AND(C27&lt;&gt;"",D27&lt;&gt;""),C27*D27,"")</f>
+        <v>8</v>
+      </c>
+      <c r="N27" s="8" t="str">
+        <f t="shared" ref="N27:N33" si="5">IF(AND(G27&lt;&gt;"",H27&lt;&gt;""),G27*H27,"")</f>
+        <v/>
+      </c>
+      <c r="O27" s="8" t="str">
+        <f t="shared" ref="O27:O33" si="6">IF(AND(I27&lt;&gt;"",J27&lt;&gt;""),I27*J27,"")</f>
+        <v/>
+      </c>
+      <c r="P27" s="8" t="str">
+        <f t="shared" ref="P27:P33" si="7">IF(AND(K27&lt;&gt;"",L27&lt;&gt;""),K27*L27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B28" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="9">
+        <v>1</v>
+      </c>
+      <c r="D28" s="9">
+        <v>2</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="16">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="N28" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O28" s="8" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="P28" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B29" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="9">
+        <v>2</v>
+      </c>
+      <c r="H29" s="9">
+        <v>2</v>
+      </c>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N29" s="16">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="O29" s="8" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="P29" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B30" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="9">
+        <v>3</v>
+      </c>
+      <c r="J30" s="9">
+        <v>2</v>
+      </c>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N30" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O30" s="13">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="P30" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B31" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="9">
+        <v>3</v>
+      </c>
+      <c r="J31" s="9">
+        <v>3</v>
+      </c>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N31" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O31" s="13">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="P31" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B32" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="9">
+        <v>2</v>
+      </c>
+      <c r="L32" s="9">
+        <v>2</v>
+      </c>
+      <c r="M32" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N32" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O32" s="8" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="P32" s="16">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B33" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="9">
+        <v>2</v>
+      </c>
+      <c r="L33" s="9">
+        <v>3</v>
+      </c>
+      <c r="M33" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N33" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O33" s="8" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="P33" s="13">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B36" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B37" s="5"/>
+      <c r="C37" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B38" s="4"/>
+      <c r="C38" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B39" s="3"/>
+      <c r="C39" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B40" s="2"/>
+      <c r="C40" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B42" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+    </row>
+    <row r="45" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="T45" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="U45" s="25"/>
+    </row>
+    <row r="47" spans="2:21" ht="290.39999999999998" x14ac:dyDescent="0.3">
+      <c r="T47" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="U47" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="T48" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="U48" s="22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="20:21" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="T49" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U49" s="22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="20:21" ht="356.4" x14ac:dyDescent="0.3">
+      <c r="T50" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50" s="22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="20:21" ht="198" x14ac:dyDescent="0.3">
+      <c r="T51" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="U51" s="22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="20:21" ht="290.39999999999998" x14ac:dyDescent="0.3">
+      <c r="T52" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="U52" s="22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="20:21" ht="237.6" x14ac:dyDescent="0.3">
+      <c r="T53" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="U53" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="20:21" ht="277.2" x14ac:dyDescent="0.3">
+      <c r="T54" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="U54" s="22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="56" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T56" s="21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T57" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T58" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T59" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T60" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B3:P3"/>
+    <mergeCell ref="B22:P22"/>
+    <mergeCell ref="B25:P25"/>
+    <mergeCell ref="B42:P42"/>
+    <mergeCell ref="T45:U45"/>
+  </mergeCells>
+  <conditionalFormatting sqref="M5:P13">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThanOrEqual">
+      <formula>15</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="between">
+      <formula>10</formula>
+      <formula>14</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="between">
+      <formula>5</formula>
+      <formula>9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="between">
+      <formula>1</formula>
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M27:P33">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">
+      <formula>15</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="between">
+      <formula>10</formula>
+      <formula>14</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="between">
+      <formula>5</formula>
+      <formula>9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="between">
+      <formula>1</formula>
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Specifications/Risk_Traceability_Matrix.xlsx
+++ b/Specifications/Risk_Traceability_Matrix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NoordWes Universiteit\Mechatronics Engineering\Jaar 3\Semester 2\MCTR327\Eng_DesignProject_GantryCrane_Group-18\Specifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C587BAA-33EE-45CB-B4E4-C5BCF3D9B3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C7C40F-A505-478C-AB18-E0303D0ECE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CE4302D-EC5D-4A58-A53C-426CE452EC11}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4CE4302D-EC5D-4A58-A53C-426CE452EC11}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="58">
-  <si>
-    <t>Table 24  Risk Traceability Matrix BEFORE Mitigation</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="53">
   <si>
     <t>Risk Codes</t>
   </si>
@@ -54,12 +51,6 @@
   </si>
   <si>
     <t>L1</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>T2</t>
   </si>
   <si>
     <t>K1</t>
@@ -90,10 +81,6 @@
 Score</t>
   </si>
   <si>
-    <t>Technical Risk
-Score</t>
-  </si>
-  <si>
     <t>Logistic Risk
 Score</t>
   </si>
@@ -110,22 +97,6 @@
 Likelihood</t>
   </si>
   <si>
-    <t>Technical Risk
-Impact</t>
-  </si>
-  <si>
-    <t>Technical Risk
-Likelihood</t>
-  </si>
-  <si>
-    <t>Logistic Risk
-Impact</t>
-  </si>
-  <si>
-    <t>Logistic Risk
-Likelihood</t>
-  </si>
-  <si>
     <t>Schedule Risk
 Impact</t>
   </si>
@@ -134,9 +105,6 @@
 Likelihood</t>
   </si>
   <si>
-    <t>Table 25  Risk Traceability Matrix AFTER Mitigation</t>
-  </si>
-  <si>
     <t>≥ 15     Critical risk</t>
   </si>
   <si>
@@ -218,27 +186,39 @@
     <t>P1</t>
   </si>
   <si>
-    <t>P Risk
-Likelihood</t>
-  </si>
-  <si>
-    <t>P Risk
-Impact</t>
-  </si>
-  <si>
     <t>Logistical Risk
 Likelihood</t>
   </si>
   <si>
     <t>Logistical Risk
 Impact</t>
+  </si>
+  <si>
+    <t>Group Risk Score</t>
+  </si>
+  <si>
+    <t>Integration Risk Score</t>
+  </si>
+  <si>
+    <t>Integration Risk
+Likelihood</t>
+  </si>
+  <si>
+    <t>Integration Risk
+Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Risk Traceability Matrix AFTER Mitigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Risk Traceability Matrix BEFORE Mitigation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,13 +248,6 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -386,7 +359,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -409,11 +382,179 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -423,9 +564,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -441,48 +579,305 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD700"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF8C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD700"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF8C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD700"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF8C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD700"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF8C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD700"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF8C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -582,6 +977,133 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>281940</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B84F693-854F-D72A-8186-80303D49C91B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8206740" y="5394960"/>
+          <a:ext cx="5775960" cy="2674620"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDD82359-7F88-EB52-8C83-6C4F2720D65A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7448550" y="323850"/>
+          <a:ext cx="5772150" cy="2828925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -901,7 +1423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEDE8F47-BC4B-4B60-A383-ABA60BBBE1EE}">
-  <dimension ref="B3:U60"/>
+  <dimension ref="B3:V60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="4.77734375" customWidth="1"/>
@@ -911,412 +1433,502 @@
     <col min="9" max="10" width="4.5546875" customWidth="1"/>
     <col min="11" max="11" width="4.6640625" customWidth="1"/>
     <col min="12" max="12" width="5.6640625" customWidth="1"/>
-    <col min="13" max="13" width="5" customWidth="1"/>
-    <col min="14" max="14" width="4.33203125" customWidth="1"/>
-    <col min="15" max="15" width="5.109375" customWidth="1"/>
-    <col min="16" max="16" width="6.21875" customWidth="1"/>
+    <col min="13" max="14" width="5" customWidth="1"/>
+    <col min="15" max="15" width="4.33203125" customWidth="1"/>
+    <col min="16" max="16" width="5.109375" customWidth="1"/>
+    <col min="17" max="17" width="6.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B3" s="23" t="s">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B3" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+    </row>
+    <row r="4" spans="2:17" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23"/>
-      <c r="P3" s="23"/>
-    </row>
-    <row r="4" spans="2:16" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="15" t="s">
+      <c r="C4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B5" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="14" t="s">
+      <c r="C5" s="8">
+        <v>5</v>
+      </c>
+      <c r="D5" s="8">
+        <v>4</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="11">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;""),C5*D5,"")</f>
         <v>20</v>
       </c>
-      <c r="H4" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="O4" s="14" t="s">
+      <c r="N5" s="11" t="str">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5*F5,"")</f>
+        <v/>
+      </c>
+      <c r="O5" s="7" t="str">
+        <f>IF(AND(G5&lt;&gt;"",H5&lt;&gt;""),G5*H5,"")</f>
+        <v/>
+      </c>
+      <c r="P5" s="7" t="str">
+        <f>IF(AND(I5&lt;&gt;"",J5&lt;&gt;""),I5*J5,"")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="7" t="str">
+        <f>IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),K5*L5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B6" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="8">
+        <v>4</v>
+      </c>
+      <c r="D6" s="8">
+        <v>4</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="11">
+        <f t="shared" ref="M6:M13" si="0">IF(AND(C6&lt;&gt;"",D6&lt;&gt;""),C6*D6,"")</f>
         <v>16</v>
       </c>
-      <c r="P4" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B5" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="9">
-        <v>5</v>
-      </c>
-      <c r="D5" s="9">
+      <c r="N6" s="11" t="str">
+        <f t="shared" ref="N6:N13" si="1">IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6*F6,"")</f>
+        <v/>
+      </c>
+      <c r="O6" s="7" t="str">
+        <f t="shared" ref="O6:O13" si="2">IF(AND(G6&lt;&gt;"",H6&lt;&gt;""),G6*H6,"")</f>
+        <v/>
+      </c>
+      <c r="P6" s="7" t="str">
+        <f t="shared" ref="P6:P13" si="3">IF(AND(I6&lt;&gt;"",J6&lt;&gt;""),I6*J6,"")</f>
+        <v/>
+      </c>
+      <c r="Q6" s="7" t="str">
+        <f t="shared" ref="Q6:Q13" si="4">IF(AND(K6&lt;&gt;"",L6&lt;&gt;""),K6*L6,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="8">
+        <v>3</v>
+      </c>
+      <c r="F7" s="8">
         <v>4</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="12">
-        <f t="shared" ref="M5:M13" si="0">IF(AND(C5&lt;&gt;"",D5&lt;&gt;""),C5*D5,"")</f>
-        <v>20</v>
-      </c>
-      <c r="N5" s="8" t="str">
-        <f t="shared" ref="N5:N13" si="1">IF(AND(G5&lt;&gt;"",H5&lt;&gt;""),G5*H5,"")</f>
-        <v/>
-      </c>
-      <c r="O5" s="8" t="str">
-        <f t="shared" ref="O5:O13" si="2">IF(AND(I5&lt;&gt;"",J5&lt;&gt;""),I5*J5,"")</f>
-        <v/>
-      </c>
-      <c r="P5" s="8" t="str">
-        <f t="shared" ref="P5:P13" si="3">IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),K5*L5,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B6" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="9">
-        <v>2</v>
-      </c>
-      <c r="D6" s="9">
-        <v>3</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="13">
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="N6" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O6" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P6" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B7" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="9">
-        <v>3</v>
-      </c>
-      <c r="H9" s="9">
-        <v>4</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N9" s="7">
+        <v/>
+      </c>
+      <c r="N7" s="11">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="O9" s="8" t="str">
+      <c r="O7" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P9" s="8" t="str">
+      <c r="P7" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
+      <c r="Q7" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B8" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="8">
+        <v>3</v>
+      </c>
+      <c r="F8" s="8">
+        <v>5</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N8" s="11">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="O8" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P8" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Q8" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="8">
+        <v>5</v>
+      </c>
+      <c r="H9" s="8">
+        <v>4</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N9" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O9" s="7">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="P9" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Q9" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B10" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="8">
+        <v>5</v>
+      </c>
+      <c r="H10" s="8">
+        <v>4</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N10" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O10" s="7">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="P10" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Q10" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B11" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="8">
+        <v>3</v>
+      </c>
+      <c r="J11" s="8">
+        <v>5</v>
+      </c>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N11" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O11" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P11" s="7">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="Q11" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B12" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="8">
+        <v>5</v>
+      </c>
+      <c r="L12" s="8">
+        <v>4</v>
+      </c>
+      <c r="M12" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N12" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O12" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P12" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Q12" s="7">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="8">
+        <v>5</v>
+      </c>
+      <c r="L13" s="8">
+        <v>4</v>
+      </c>
+      <c r="M13" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N13" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O13" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P13" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Q13" s="7">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="39"/>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B17" s="36"/>
+      <c r="C17" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="38"/>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B18" s="24"/>
+      <c r="C18" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10">
-        <v>4</v>
-      </c>
-      <c r="J10" s="10">
-        <v>4</v>
-      </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N10" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O10" s="12">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-      <c r="P10" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B11" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="9">
-        <v>3</v>
-      </c>
-      <c r="J11" s="9">
-        <v>5</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N11" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O11" s="12">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="P11" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B12" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="9">
-        <v>3</v>
-      </c>
-      <c r="L12" s="9">
-        <v>4</v>
-      </c>
-      <c r="M12" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N12" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O12" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P12" s="7">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B13" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="9">
-        <v>3</v>
-      </c>
-      <c r="L13" s="9">
-        <v>4</v>
-      </c>
-      <c r="M13" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N13" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O13" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P13" s="7">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B16" s="6" t="s">
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="29"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B19" s="25"/>
+      <c r="C19" s="28" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B17" s="5"/>
-      <c r="C17" s="1" t="s">
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="29"/>
+    </row>
+    <row r="20" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="26"/>
+      <c r="C20" s="30" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B18" s="4"/>
-      <c r="C18" s="1" t="s">
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="32"/>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B22" s="21" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B19" s="3"/>
-      <c r="C19" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B20" s="2"/>
-      <c r="C20" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B22" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B25" s="23" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C25" s="23"/>
       <c r="D25" s="23"/>
@@ -1332,480 +1944,596 @@
       <c r="N25" s="23"/>
       <c r="O25" s="23"/>
       <c r="P25" s="23"/>
-    </row>
-    <row r="26" spans="2:16" ht="65.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B26" s="15" t="s">
+      <c r="Q25" s="23"/>
+    </row>
+    <row r="26" spans="2:17" ht="66" x14ac:dyDescent="0.3">
+      <c r="B26" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q26" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B27" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C26" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L26" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M26" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="N26" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="O26" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="P26" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B27" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" s="9">
-        <v>2</v>
-      </c>
-      <c r="D27" s="9">
+      <c r="C27" s="8">
         <v>4</v>
+      </c>
+      <c r="D27" s="8">
+        <v>3</v>
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="13">
-        <f t="shared" ref="M27:M33" si="4">IF(AND(C27&lt;&gt;"",D27&lt;&gt;""),C27*D27,"")</f>
-        <v>8</v>
-      </c>
-      <c r="N27" s="8" t="str">
-        <f t="shared" ref="N27:N33" si="5">IF(AND(G27&lt;&gt;"",H27&lt;&gt;""),G27*H27,"")</f>
-        <v/>
-      </c>
-      <c r="O27" s="8" t="str">
-        <f t="shared" ref="O27:O33" si="6">IF(AND(I27&lt;&gt;"",J27&lt;&gt;""),I27*J27,"")</f>
-        <v/>
-      </c>
-      <c r="P27" s="8" t="str">
-        <f t="shared" ref="P27:P33" si="7">IF(AND(K27&lt;&gt;"",L27&lt;&gt;""),K27*L27,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B28" s="11" t="s">
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="11">
+        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;""),C27*D27,"")</f>
+        <v>12</v>
+      </c>
+      <c r="N27" s="11" t="str">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27*F27,"")</f>
+        <v/>
+      </c>
+      <c r="O27" s="7" t="str">
+        <f>IF(AND(G27&lt;&gt;"",H27&lt;&gt;""),G27*H27,"")</f>
+        <v/>
+      </c>
+      <c r="P27" s="7" t="str">
+        <f>IF(AND(I27&lt;&gt;"",J27&lt;&gt;""),I27*J27,"")</f>
+        <v/>
+      </c>
+      <c r="Q27" s="7" t="str">
+        <f>IF(AND(K27&lt;&gt;"",L27&lt;&gt;""),K27*L27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B28" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="8">
+        <v>2</v>
+      </c>
+      <c r="D28" s="8">
         <v>3</v>
-      </c>
-      <c r="C28" s="9">
-        <v>1</v>
-      </c>
-      <c r="D28" s="9">
-        <v>2</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="16">
-        <f t="shared" si="4"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="11">
+        <f t="shared" ref="M28:M35" si="5">IF(AND(C28&lt;&gt;"",D28&lt;&gt;""),C28*D28,"")</f>
+        <v>6</v>
+      </c>
+      <c r="N28" s="11" t="str">
+        <f t="shared" ref="N28:N35" si="6">IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28*F28,"")</f>
+        <v/>
+      </c>
+      <c r="O28" s="7" t="str">
+        <f t="shared" ref="O28:O35" si="7">IF(AND(G28&lt;&gt;"",H28&lt;&gt;""),G28*H28,"")</f>
+        <v/>
+      </c>
+      <c r="P28" s="7" t="str">
+        <f t="shared" ref="P28:P35" si="8">IF(AND(I28&lt;&gt;"",J28&lt;&gt;""),I28*J28,"")</f>
+        <v/>
+      </c>
+      <c r="Q28" s="7" t="str">
+        <f t="shared" ref="Q28:Q35" si="9">IF(AND(K28&lt;&gt;"",L28&lt;&gt;""),K28*L28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B29" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="8">
         <v>2</v>
       </c>
-      <c r="N28" s="8" t="str">
+      <c r="F29" s="8">
+        <v>3</v>
+      </c>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="O28" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="P28" s="8" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B29" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="9">
-        <v>2</v>
-      </c>
-      <c r="H29" s="9">
-        <v>2</v>
-      </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="N29" s="16">
-        <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="O29" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="P29" s="8" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B30" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="9">
-        <v>3</v>
-      </c>
-      <c r="J30" s="9">
-        <v>2</v>
-      </c>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="N30" s="8" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="O30" s="13">
+      <c r="N29" s="11">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="P30" s="8" t="str">
+      <c r="O29" s="7" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-    </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="9">
-        <v>3</v>
-      </c>
-      <c r="J31" s="9">
-        <v>3</v>
-      </c>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="N31" s="8" t="str">
+      <c r="P29" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="Q29" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B30" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="8">
+        <v>2</v>
+      </c>
+      <c r="F30" s="8">
+        <v>5</v>
+      </c>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="O31" s="13">
+      <c r="N30" s="11">
         <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="P31" s="8" t="str">
+        <v>10</v>
+      </c>
+      <c r="O30" s="7" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-    </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B32" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="9">
+      <c r="P30" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="Q30" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="8">
         <v>2</v>
       </c>
-      <c r="L32" s="9">
+      <c r="H31" s="8">
         <v>2</v>
       </c>
-      <c r="M32" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="N32" s="8" t="str">
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="O32" s="8" t="str">
+      <c r="N31" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P32" s="16">
+      <c r="O31" s="7">
+        <f>IF(AND(G31&lt;&gt;"",H31&lt;&gt;""),G31*H31,"")</f>
+        <v>4</v>
+      </c>
+      <c r="P31" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="Q31" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B32" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="8">
+        <v>2</v>
+      </c>
+      <c r="H32" s="8">
+        <v>2</v>
+      </c>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="N32" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="O32" s="7">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B33" s="11" t="s">
+      <c r="P32" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="Q32" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B33" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="8">
+        <v>2</v>
+      </c>
+      <c r="J33" s="8">
+        <v>4</v>
+      </c>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="N33" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="O33" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="P33" s="7">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="9">
+      <c r="Q33" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B34" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="8">
         <v>2</v>
       </c>
-      <c r="L33" s="9">
+      <c r="L34" s="8">
+        <v>2</v>
+      </c>
+      <c r="M34" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="N34" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="O34" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="P34" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="Q34" s="7">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B35" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="8">
         <v>3</v>
       </c>
-      <c r="M33" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="N33" s="8" t="str">
+      <c r="L35" s="8">
+        <v>3</v>
+      </c>
+      <c r="M35" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="O33" s="8" t="str">
+      <c r="N35" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P33" s="13">
+      <c r="O35" s="7" t="str">
         <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="P35" s="7" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="Q35" s="7">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B36" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B36" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B37" s="5"/>
       <c r="C37" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B38" s="4"/>
       <c r="C38" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B39" s="3"/>
       <c r="C39" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B40" s="2"/>
       <c r="C40" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B42" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="24"/>
-    </row>
-    <row r="45" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="T45" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="U45" s="25"/>
-    </row>
-    <row r="47" spans="2:21" ht="290.39999999999998" x14ac:dyDescent="0.3">
-      <c r="T47" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="U47" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="2:21" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="T48" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="U48" s="22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="20:21" ht="184.8" x14ac:dyDescent="0.3">
-      <c r="T49" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U49" s="22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="50" spans="20:21" ht="356.4" x14ac:dyDescent="0.3">
-      <c r="T50" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="U50" s="22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="20:21" ht="198" x14ac:dyDescent="0.3">
-      <c r="T51" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="U51" s="22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="21"/>
+      <c r="L42" s="21"/>
+      <c r="M42" s="21"/>
+      <c r="N42" s="21"/>
+      <c r="O42" s="21"/>
+      <c r="P42" s="21"/>
+      <c r="Q42" s="21"/>
+    </row>
+    <row r="45" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="U45" s="22" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="52" spans="20:21" ht="290.39999999999998" x14ac:dyDescent="0.3">
-      <c r="T52" s="21" t="s">
+      <c r="V45" s="22"/>
+    </row>
+    <row r="47" spans="2:22" ht="290.39999999999998" x14ac:dyDescent="0.3">
+      <c r="U47" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="V47" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="U52" s="22" t="s">
+    </row>
+    <row r="48" spans="2:22" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="U48" s="18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="53" spans="20:21" ht="237.6" x14ac:dyDescent="0.3">
-      <c r="T53" s="21" t="s">
+      <c r="V48" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="U53" s="22" t="s">
+    </row>
+    <row r="49" spans="21:22" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="U49" s="18" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="54" spans="20:21" ht="277.2" x14ac:dyDescent="0.3">
-      <c r="T54" s="21" t="s">
+      <c r="V49" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="U54" s="22" t="s">
+    </row>
+    <row r="50" spans="21:22" ht="356.4" x14ac:dyDescent="0.3">
+      <c r="U50" s="18" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="56" spans="20:21" x14ac:dyDescent="0.3">
-      <c r="T56" s="21" t="s">
+      <c r="V50" s="19" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="20:21" x14ac:dyDescent="0.3">
-      <c r="T57" s="20" t="s">
+    <row r="51" spans="21:22" ht="198" x14ac:dyDescent="0.3">
+      <c r="U51" s="18" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="58" spans="20:21" x14ac:dyDescent="0.3">
-      <c r="T58" s="19" t="s">
+      <c r="V51" s="19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="20:21" x14ac:dyDescent="0.3">
-      <c r="T59" s="18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="20:21" x14ac:dyDescent="0.3">
-      <c r="T60" s="17" t="s">
+    <row r="52" spans="21:22" ht="290.39999999999998" x14ac:dyDescent="0.3">
+      <c r="U52" s="18" t="s">
         <v>28</v>
+      </c>
+      <c r="V52" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="21:22" ht="237.6" x14ac:dyDescent="0.3">
+      <c r="U53" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="V53" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="21:22" ht="277.2" x14ac:dyDescent="0.3">
+      <c r="U54" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="V54" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="21:22" x14ac:dyDescent="0.3">
+      <c r="U56" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="21:22" x14ac:dyDescent="0.3">
+      <c r="U57" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="21:22" x14ac:dyDescent="0.3">
+      <c r="U58" s="16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="21:22" x14ac:dyDescent="0.3">
+      <c r="U59" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="21:22" x14ac:dyDescent="0.3">
+      <c r="U60" s="14" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B3:P3"/>
-    <mergeCell ref="B22:P22"/>
-    <mergeCell ref="B25:P25"/>
-    <mergeCell ref="B42:P42"/>
-    <mergeCell ref="T45:U45"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="B22:Q22"/>
+    <mergeCell ref="B25:Q25"/>
+    <mergeCell ref="B42:Q42"/>
+    <mergeCell ref="U45:V45"/>
   </mergeCells>
-  <conditionalFormatting sqref="M5:P13">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="M5:Q13">
+    <cfRule type="cellIs" dxfId="27" priority="13" operator="greaterThanOrEqual">
       <formula>15</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="26" priority="14" operator="between">
       <formula>10</formula>
       <formula>14</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="25" priority="15" operator="between">
       <formula>5</formula>
       <formula>9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="24" priority="16" operator="between">
       <formula>1</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M27:P33">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="M27:Q35">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="greaterThanOrEqual">
       <formula>15</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="between">
       <formula>10</formula>
       <formula>14</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="between">
       <formula>5</formula>
       <formula>9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="between">
       <formula>1</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Specifications/Risk_Traceability_Matrix.xlsx
+++ b/Specifications/Risk_Traceability_Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NoordWes Universiteit\Mechatronics Engineering\Jaar 3\Semester 2\MCTR327\Eng_DesignProject_GantryCrane_Group-18\Specifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C7C40F-A505-478C-AB18-E0303D0ECE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CC94B6-92C0-4187-BF3F-C5D59B8E1B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4CE4302D-EC5D-4A58-A53C-426CE452EC11}"/>
   </bookViews>
@@ -1045,15 +1045,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>169545</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1083,8 +1083,69 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7448550" y="323850"/>
-          <a:ext cx="5772150" cy="2828925"/>
+          <a:off x="7410450" y="350520"/>
+          <a:ext cx="5768340" cy="2830830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>93345</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>234315</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D769C49-B3D0-70EA-50BF-498CA0B3DDCB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="13790295" y="649605"/>
+          <a:ext cx="1969770" cy="933450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
